--- a/results/reports/year_2023_report.xlsx
+++ b/results/reports/year_2023_report.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,30 +505,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -572,21 +582,27 @@
         <v>69.91</v>
       </c>
       <c r="M2" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="N2" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="O2" t="n">
         <v>20.55</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>33.03</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>17.26</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>7.09</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>-6.41</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>9.890000000000001</v>
       </c>
     </row>
@@ -667,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6768909645357425</v>
+        <v>0.6768909645357426</v>
       </c>
       <c r="E3" t="n">
         <v>3.5836</v>
@@ -727,7 +743,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6446713710311536</v>
+        <v>0.6446713710311538</v>
       </c>
       <c r="E6" t="n">
         <v>-3.7333</v>
@@ -847,7 +863,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6306163258556665</v>
+        <v>0.6306163258556666</v>
       </c>
       <c r="E12" t="n">
         <v>-0.404</v>
@@ -927,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6240659576022884</v>
+        <v>0.6240659576022883</v>
       </c>
       <c r="E16" t="n">
         <v>3.896</v>
@@ -967,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6174135621422447</v>
+        <v>0.6174135621422449</v>
       </c>
       <c r="E18" t="n">
         <v>1.2205</v>
@@ -987,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6152303617589598</v>
+        <v>0.6152303617589597</v>
       </c>
       <c r="E19" t="n">
         <v>14.3939</v>
@@ -1007,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6145131260028309</v>
+        <v>0.6145131260028307</v>
       </c>
       <c r="E20" t="n">
         <v>3.6483</v>
@@ -1113,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6810700445173342</v>
+        <v>0.6810700445173343</v>
       </c>
       <c r="E3" t="n">
         <v>17.8133</v>
@@ -1153,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6578335543160582</v>
+        <v>0.6578335543160579</v>
       </c>
       <c r="E5" t="n">
         <v>1.8706</v>
@@ -1193,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6516927621061359</v>
+        <v>0.6516927621061357</v>
       </c>
       <c r="E7" t="n">
         <v>2.1424</v>
@@ -1233,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6481902691372154</v>
+        <v>0.6481902691372153</v>
       </c>
       <c r="E9" t="n">
         <v>-2.0464</v>
@@ -1273,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6419731859582236</v>
+        <v>0.6419731859582238</v>
       </c>
       <c r="E11" t="n">
         <v>3.195</v>
@@ -1333,7 +1349,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6345538761034261</v>
+        <v>0.6345538761034262</v>
       </c>
       <c r="E14" t="n">
         <v>3.5646</v>
@@ -1393,7 +1409,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6291551632602165</v>
+        <v>0.6291551632602164</v>
       </c>
       <c r="E17" t="n">
         <v>1.0546</v>
@@ -1473,7 +1489,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.624315696718451</v>
+        <v>0.6243156967184509</v>
       </c>
       <c r="E21" t="n">
         <v>1.1716</v>
@@ -1599,7 +1615,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6796744925820133</v>
+        <v>0.6796744925820132</v>
       </c>
       <c r="E5" t="n">
         <v>1.4091</v>
@@ -1659,7 +1675,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6636561994670438</v>
+        <v>0.6636561994670437</v>
       </c>
       <c r="E8" t="n">
         <v>1.2986</v>
@@ -1679,7 +1695,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6618085911592045</v>
+        <v>0.6618085911592047</v>
       </c>
       <c r="E9" t="n">
         <v>-1.7929</v>
@@ -1699,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6607942147437804</v>
+        <v>0.6607942147437805</v>
       </c>
       <c r="E10" t="n">
         <v>-0.9519</v>
@@ -1759,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6550090283565431</v>
+        <v>0.6550090283565432</v>
       </c>
       <c r="E13" t="n">
         <v>-1.5517</v>
@@ -1779,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6523600133488828</v>
+        <v>0.6523600133488827</v>
       </c>
       <c r="E14" t="n">
         <v>-4.4298</v>
@@ -1799,7 +1815,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6519666660255232</v>
+        <v>0.6519666660255234</v>
       </c>
       <c r="E15" t="n">
         <v>-1.9407</v>
@@ -1819,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6477129762436911</v>
+        <v>0.6477129762436913</v>
       </c>
       <c r="E16" t="n">
         <v>10.3524</v>
@@ -1839,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6473026281811803</v>
+        <v>0.6473026281811805</v>
       </c>
       <c r="E17" t="n">
         <v>0.3934</v>
@@ -1859,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6458156225274437</v>
+        <v>0.645815622527444</v>
       </c>
       <c r="E18" t="n">
         <v>-9.2056</v>
@@ -1899,7 +1915,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6422519559674821</v>
+        <v>0.642251955967482</v>
       </c>
       <c r="E20" t="n">
         <v>-3.9025</v>
@@ -1919,7 +1935,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6399705006909658</v>
+        <v>0.6399705006909657</v>
       </c>
       <c r="E21" t="n">
         <v>-4.164</v>
@@ -2005,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7273033911862941</v>
+        <v>0.7273033911862942</v>
       </c>
       <c r="E3" t="n">
         <v>26.0108</v>
@@ -2125,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6850409122704277</v>
+        <v>0.6850409122704276</v>
       </c>
       <c r="E9" t="n">
         <v>5.3333</v>
@@ -2185,7 +2201,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6667728353133642</v>
+        <v>0.6667728353133643</v>
       </c>
       <c r="E12" t="n">
         <v>-5.3237</v>
@@ -2205,7 +2221,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6653793821244196</v>
+        <v>0.6653793821244194</v>
       </c>
       <c r="E13" t="n">
         <v>3.1537</v>
@@ -2245,7 +2261,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6604617414666675</v>
+        <v>0.6604617414666676</v>
       </c>
       <c r="E15" t="n">
         <v>6.3188</v>
@@ -2345,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6470691514393281</v>
+        <v>0.6470691514393279</v>
       </c>
       <c r="E20" t="n">
         <v>-1.7964</v>
@@ -2491,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6755804101474054</v>
+        <v>0.6755804101474052</v>
       </c>
       <c r="E5" t="n">
         <v>6.4188</v>
@@ -2511,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6739993652663521</v>
+        <v>0.6739993652663522</v>
       </c>
       <c r="E6" t="n">
         <v>8.992699999999999</v>
@@ -2591,7 +2607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6541610735038762</v>
+        <v>0.6541610735038761</v>
       </c>
       <c r="E10" t="n">
         <v>10.7814</v>
@@ -2651,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6487764907334258</v>
+        <v>0.6487764907334257</v>
       </c>
       <c r="E13" t="n">
         <v>3.5943</v>
@@ -2691,7 +2707,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6431651676673501</v>
+        <v>0.6431651676673499</v>
       </c>
       <c r="E15" t="n">
         <v>6.8731</v>
@@ -2711,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6430438674754275</v>
+        <v>0.6430438674754276</v>
       </c>
       <c r="E16" t="n">
         <v>8.190300000000001</v>
@@ -2751,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6337271263842941</v>
+        <v>0.633727126384294</v>
       </c>
       <c r="E18" t="n">
         <v>20.9243</v>
@@ -2877,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7164118035899759</v>
+        <v>0.7164118035899757</v>
       </c>
       <c r="E2" t="n">
         <v>10.7741</v>
@@ -2917,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6983909997064919</v>
+        <v>0.698390999706492</v>
       </c>
       <c r="E4" t="n">
         <v>1.8452</v>
@@ -3017,7 +3033,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.640268919220524</v>
+        <v>0.6402689192205239</v>
       </c>
       <c r="E9" t="n">
         <v>7.5781</v>
@@ -3037,7 +3053,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6400747176260289</v>
+        <v>0.6400747176260287</v>
       </c>
       <c r="E10" t="n">
         <v>2.3933</v>
@@ -3057,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6327229434457806</v>
+        <v>0.6327229434457805</v>
       </c>
       <c r="E11" t="n">
         <v>12.7411</v>
@@ -3137,7 +3153,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6283961285028269</v>
+        <v>0.6283961285028268</v>
       </c>
       <c r="E15" t="n">
         <v>9.603899999999999</v>
@@ -3177,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6251278856670056</v>
+        <v>0.6251278856670055</v>
       </c>
       <c r="E17" t="n">
         <v>-1.9489</v>
@@ -3197,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6219480685204434</v>
+        <v>0.6219480685204435</v>
       </c>
       <c r="E18" t="n">
         <v>0.7576000000000001</v>
@@ -3277,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,25 +3314,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -3333,18 +3354,21 @@
         <v>9.699999999999999</v>
       </c>
       <c r="D2" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="E2" t="n">
         <v>3.37</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>7.59</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>-0.13</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -3359,18 +3383,21 @@
         <v>1.68</v>
       </c>
       <c r="D3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E3" t="n">
         <v>-1.41</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4.82</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1.79</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -3385,18 +3412,21 @@
         <v>2.8</v>
       </c>
       <c r="D4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E4" t="n">
         <v>1.78</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.55</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>-4.96</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>-3.82</v>
       </c>
     </row>
@@ -3411,18 +3441,21 @@
         <v>-0.24</v>
       </c>
       <c r="D5" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="E5" t="n">
         <v>-2.77</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2.11</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1.58</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-0.58</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -3437,18 +3470,21 @@
         <v>5.96</v>
       </c>
       <c r="D6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E6" t="n">
         <v>2.92</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-1.57</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-0.87</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-6.04</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-2.27</v>
       </c>
     </row>
@@ -3463,18 +3499,21 @@
         <v>1.24</v>
       </c>
       <c r="D7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E7" t="n">
         <v>1.61</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3.35</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.78</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-0.97</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -3489,18 +3528,21 @@
         <v>2.66</v>
       </c>
       <c r="D8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E8" t="n">
         <v>-0.25</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-2.55</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-0.39</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.54</v>
       </c>
     </row>
@@ -3515,18 +3557,21 @@
         <v>1.85</v>
       </c>
       <c r="D9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E9" t="n">
         <v>1.49</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-2.94</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-4.05</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-0.21</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.86</v>
       </c>
     </row>
@@ -3541,18 +3586,21 @@
         <v>-0.11</v>
       </c>
       <c r="D10" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E10" t="n">
         <v>-0.96</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-1.34</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-2.06</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>2.82</v>
       </c>
     </row>
@@ -3567,18 +3615,21 @@
         <v>3.75</v>
       </c>
       <c r="D11" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E11" t="n">
         <v>4.81</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-4.74</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-3.53</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-0.77</v>
       </c>
     </row>
@@ -3593,18 +3644,21 @@
         <v>8.640000000000001</v>
       </c>
       <c r="D12" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="E12" t="n">
         <v>5.25</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>7.55</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>6.69</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>6.31</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1.78</v>
       </c>
     </row>
@@ -3619,18 +3673,21 @@
         <v>8.99</v>
       </c>
       <c r="D13" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="E13" t="n">
         <v>3.33</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>7.33</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>5.37</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>3.13</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -3917,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6701328279678725</v>
+        <v>0.6701328279678723</v>
       </c>
       <c r="E2" t="n">
         <v>14.8148</v>
@@ -3937,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6581899335493189</v>
+        <v>0.6581899335493188</v>
       </c>
       <c r="E3" t="n">
         <v>23.0218</v>
@@ -4017,7 +4074,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6408925198564749</v>
+        <v>0.6408925198564751</v>
       </c>
       <c r="E7" t="n">
         <v>0.4777</v>
@@ -4037,7 +4094,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6360217776431228</v>
+        <v>0.636021777643123</v>
       </c>
       <c r="E8" t="n">
         <v>17.129</v>
@@ -4077,7 +4134,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6327553375519637</v>
+        <v>0.6327553375519636</v>
       </c>
       <c r="E10" t="n">
         <v>-3.6518</v>
@@ -4117,7 +4174,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6258577870467003</v>
+        <v>0.6258577870467001</v>
       </c>
       <c r="E12" t="n">
         <v>8.226900000000001</v>
@@ -4137,7 +4194,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6246955896070809</v>
+        <v>0.6246955896070808</v>
       </c>
       <c r="E13" t="n">
         <v>2.4499</v>
@@ -4197,7 +4254,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6205751460016197</v>
+        <v>0.6205751460016196</v>
       </c>
       <c r="E16" t="n">
         <v>-0.543</v>
@@ -4403,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.693151131519447</v>
+        <v>0.6931511315194469</v>
       </c>
       <c r="E4" t="n">
         <v>2.8636</v>
@@ -4543,7 +4600,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6182918108478371</v>
+        <v>0.618291810847837</v>
       </c>
       <c r="E11" t="n">
         <v>-16.536</v>
@@ -4703,7 +4760,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6111333127570793</v>
+        <v>0.6111333127570792</v>
       </c>
       <c r="E19" t="n">
         <v>-2.1465</v>
@@ -4889,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6164715343030921</v>
+        <v>0.6164715343030922</v>
       </c>
       <c r="E6" t="n">
         <v>-1.9444</v>
@@ -4929,7 +4986,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6119997201229783</v>
+        <v>0.6119997201229782</v>
       </c>
       <c r="E8" t="n">
         <v>-0.5464</v>
@@ -4969,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6070597116317502</v>
+        <v>0.6070597116317501</v>
       </c>
       <c r="E10" t="n">
         <v>0.4653</v>
@@ -5009,7 +5066,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6060469449438212</v>
+        <v>0.6060469449438211</v>
       </c>
       <c r="E12" t="n">
         <v>-7.1632</v>
@@ -5109,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6008104440157328</v>
+        <v>0.6008104440157327</v>
       </c>
       <c r="E17" t="n">
         <v>0.8974</v>
@@ -5129,7 +5186,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6002875638193652</v>
+        <v>0.6002875638193651</v>
       </c>
       <c r="E18" t="n">
         <v>1.5948</v>
@@ -5149,7 +5206,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6002557000981713</v>
+        <v>0.6002557000981712</v>
       </c>
       <c r="E19" t="n">
         <v>11.1111</v>
@@ -5189,7 +5246,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5989595921296486</v>
+        <v>0.5989595921296487</v>
       </c>
       <c r="E21" t="n">
         <v>11.0684</v>
@@ -5315,7 +5372,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6252634101084248</v>
+        <v>0.6252634101084247</v>
       </c>
       <c r="E5" t="n">
         <v>1.2653</v>
@@ -5335,7 +5392,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6212661513283735</v>
+        <v>0.6212661513283736</v>
       </c>
       <c r="E6" t="n">
         <v>-11.1624</v>
@@ -5375,7 +5432,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6182365241587864</v>
+        <v>0.6182365241587863</v>
       </c>
       <c r="E8" t="n">
         <v>-6.0203</v>
@@ -5455,7 +5512,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6157477401323458</v>
+        <v>0.6157477401323457</v>
       </c>
       <c r="E12" t="n">
         <v>1.8062</v>
@@ -5495,7 +5552,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6145153156397485</v>
+        <v>0.6145153156397486</v>
       </c>
       <c r="E14" t="n">
         <v>0.4653</v>
@@ -5701,7 +5758,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7185221359916381</v>
+        <v>0.7185221359916382</v>
       </c>
       <c r="E2" t="n">
         <v>29.9202</v>
@@ -5801,7 +5858,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6382719960994763</v>
+        <v>0.6382719960994762</v>
       </c>
       <c r="E7" t="n">
         <v>-0.3681</v>
@@ -6021,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6237274577168135</v>
+        <v>0.6237274577168136</v>
       </c>
       <c r="E18" t="n">
         <v>2.5253</v>
@@ -6041,7 +6098,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6226517324507889</v>
+        <v>0.622651732450789</v>
       </c>
       <c r="E19" t="n">
         <v>11.4803</v>
@@ -6081,7 +6138,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6192863392847094</v>
+        <v>0.6192863392847093</v>
       </c>
       <c r="E21" t="n">
         <v>2.5357</v>
@@ -6187,7 +6244,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6562785493366308</v>
+        <v>0.6562785493366309</v>
       </c>
       <c r="E4" t="n">
         <v>36.5337</v>
@@ -6227,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6473121952324683</v>
+        <v>0.6473121952324685</v>
       </c>
       <c r="E6" t="n">
         <v>0.2667</v>
@@ -6247,7 +6304,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6462150926000386</v>
+        <v>0.6462150926000385</v>
       </c>
       <c r="E7" t="n">
         <v>-12.8983</v>
@@ -6287,7 +6344,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6439735751831173</v>
+        <v>0.6439735751831174</v>
       </c>
       <c r="E9" t="n">
         <v>3.6865</v>
@@ -6347,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6347524087875428</v>
+        <v>0.6347524087875427</v>
       </c>
       <c r="E12" t="n">
         <v>3.0182</v>
@@ -6407,7 +6464,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6273118271356176</v>
+        <v>0.6273118271356175</v>
       </c>
       <c r="E15" t="n">
         <v>-1.9953</v>
@@ -6447,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6225147972735466</v>
+        <v>0.6225147972735467</v>
       </c>
       <c r="E17" t="n">
         <v>-2.291</v>
@@ -6507,7 +6564,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6165196425158272</v>
+        <v>0.6165196425158274</v>
       </c>
       <c r="E20" t="n">
         <v>4.336</v>

--- a/results/reports/year_2023_report.xlsx
+++ b/results/reports/year_2023_report.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6557624896387574</v>
+        <v>0.6557624896387573</v>
       </c>
       <c r="E5" t="n">
         <v>7.5</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.642720079957992</v>
+        <v>0.6427200799579919</v>
       </c>
       <c r="E7" t="n">
         <v>0.0246</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6313900942822022</v>
+        <v>0.6313900942822023</v>
       </c>
       <c r="E11" t="n">
         <v>-4.3376</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6259058206087379</v>
+        <v>0.6259058206087378</v>
       </c>
       <c r="E15" t="n">
         <v>5.1296</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6238255883323252</v>
+        <v>0.6238255883323253</v>
       </c>
       <c r="E17" t="n">
         <v>21.7178</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6152303617589597</v>
+        <v>0.6152303617589598</v>
       </c>
       <c r="E19" t="n">
         <v>14.3939</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6145131260028307</v>
+        <v>0.6145131260028309</v>
       </c>
       <c r="E20" t="n">
         <v>3.6483</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6578335543160579</v>
+        <v>0.6578335543160582</v>
       </c>
       <c r="E5" t="n">
         <v>1.8706</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.654434605519277</v>
+        <v>0.6544346055192769</v>
       </c>
       <c r="E6" t="n">
         <v>-25.0672</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6356739032283467</v>
+        <v>0.6356739032283468</v>
       </c>
       <c r="E12" t="n">
         <v>0.0055</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6291551632602164</v>
+        <v>0.6291551632602165</v>
       </c>
       <c r="E17" t="n">
         <v>1.0546</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6243156967184509</v>
+        <v>0.624315696718451</v>
       </c>
       <c r="E21" t="n">
         <v>1.1716</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7071030571581224</v>
+        <v>0.7071030571581223</v>
       </c>
       <c r="E3" t="n">
         <v>-1.4945</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6835740078668384</v>
+        <v>0.6835740078668385</v>
       </c>
       <c r="E4" t="n">
         <v>0.2311</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6796744925820132</v>
+        <v>0.6796744925820133</v>
       </c>
       <c r="E5" t="n">
         <v>1.4091</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6636561994670437</v>
+        <v>0.6636561994670438</v>
       </c>
       <c r="E8" t="n">
         <v>1.2986</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6618085911592047</v>
+        <v>0.6618085911592045</v>
       </c>
       <c r="E9" t="n">
         <v>-1.7929</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6607942147437805</v>
+        <v>0.6607942147437804</v>
       </c>
       <c r="E10" t="n">
         <v>-0.9519</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6590737076671259</v>
+        <v>0.6590737076671257</v>
       </c>
       <c r="E11" t="n">
         <v>-2.2922</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6573237384781005</v>
+        <v>0.6573237384781007</v>
       </c>
       <c r="E12" t="n">
         <v>-1.5842</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6550090283565432</v>
+        <v>0.6550090283565431</v>
       </c>
       <c r="E13" t="n">
         <v>-1.5517</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6523600133488827</v>
+        <v>0.6523600133488828</v>
       </c>
       <c r="E14" t="n">
         <v>-4.4298</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.642251955967482</v>
+        <v>0.6422519559674821</v>
       </c>
       <c r="E20" t="n">
         <v>-3.9025</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6399705006909657</v>
+        <v>0.6399705006909658</v>
       </c>
       <c r="E21" t="n">
         <v>-4.164</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7069626671565216</v>
+        <v>0.7069626671565215</v>
       </c>
       <c r="E4" t="n">
         <v>17.292</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7049426620704717</v>
+        <v>0.7049426620704718</v>
       </c>
       <c r="E5" t="n">
         <v>1.7172</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6703433882631999</v>
+        <v>0.6703433882632001</v>
       </c>
       <c r="E11" t="n">
         <v>-5.6868</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6653793821244194</v>
+        <v>0.6653793821244196</v>
       </c>
       <c r="E13" t="n">
         <v>3.1537</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6470691514393279</v>
+        <v>0.6470691514393281</v>
       </c>
       <c r="E20" t="n">
         <v>-1.7964</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.644363607372002</v>
+        <v>0.6443636073720022</v>
       </c>
       <c r="E21" t="n">
         <v>1.6573</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6692266413980321</v>
+        <v>0.6692266413980323</v>
       </c>
       <c r="E7" t="n">
         <v>4.7088</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.655190987359527</v>
+        <v>0.6551909873595271</v>
       </c>
       <c r="E9" t="n">
         <v>12.9084</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6523812325656972</v>
+        <v>0.652381232565697</v>
       </c>
       <c r="E11" t="n">
         <v>9.3207</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6504288262724245</v>
+        <v>0.6504288262724244</v>
       </c>
       <c r="E12" t="n">
         <v>4.8757</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6430438674754276</v>
+        <v>0.6430438674754275</v>
       </c>
       <c r="E16" t="n">
         <v>8.190300000000001</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6354468549706317</v>
+        <v>0.6354468549706316</v>
       </c>
       <c r="E17" t="n">
         <v>7.059</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.633727126384294</v>
+        <v>0.6337271263842941</v>
       </c>
       <c r="E18" t="n">
         <v>20.9243</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6294837163996151</v>
+        <v>0.6294837163996152</v>
       </c>
       <c r="E20" t="n">
         <v>1.897</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7164118035899757</v>
+        <v>0.7164118035899759</v>
       </c>
       <c r="E2" t="n">
         <v>10.7741</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.698390999706492</v>
+        <v>0.6983909997064919</v>
       </c>
       <c r="E4" t="n">
         <v>1.8452</v>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6402689192205239</v>
+        <v>0.640268919220524</v>
       </c>
       <c r="E9" t="n">
         <v>7.5781</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6314211026624874</v>
+        <v>0.6314211026624873</v>
       </c>
       <c r="E12" t="n">
         <v>1.4367</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6297994076174556</v>
+        <v>0.6297994076174557</v>
       </c>
       <c r="E14" t="n">
         <v>2.8758</v>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6283961285028268</v>
+        <v>0.6283961285028269</v>
       </c>
       <c r="E15" t="n">
         <v>9.603899999999999</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6265492272360805</v>
+        <v>0.6265492272360806</v>
       </c>
       <c r="E16" t="n">
         <v>2.0893</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6251278856670055</v>
+        <v>0.6251278856670056</v>
       </c>
       <c r="E17" t="n">
         <v>-1.9489</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6196470325976841</v>
+        <v>0.6196470325976839</v>
       </c>
       <c r="E20" t="n">
         <v>3.1328</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6581899335493188</v>
+        <v>0.6581899335493189</v>
       </c>
       <c r="E3" t="n">
         <v>23.0218</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6408925198564751</v>
+        <v>0.6408925198564749</v>
       </c>
       <c r="E7" t="n">
         <v>0.4777</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.636021777643123</v>
+        <v>0.6360217776431228</v>
       </c>
       <c r="E8" t="n">
         <v>17.129</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6346123340166648</v>
+        <v>0.6346123340166647</v>
       </c>
       <c r="E9" t="n">
         <v>13.0849</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6233017686448502</v>
+        <v>0.6233017686448501</v>
       </c>
       <c r="E14" t="n">
         <v>8.9649</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6220144789403459</v>
+        <v>0.6220144789403458</v>
       </c>
       <c r="E15" t="n">
         <v>15.627</v>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.618291810847837</v>
+        <v>0.6182918108478371</v>
       </c>
       <c r="E11" t="n">
         <v>-16.536</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6137733103935864</v>
+        <v>0.6137733103935863</v>
       </c>
       <c r="E15" t="n">
         <v>2.2634</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6599173622480276</v>
+        <v>0.6599173622480277</v>
       </c>
       <c r="E3" t="n">
         <v>2.0305</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6164715343030922</v>
+        <v>0.616471534303092</v>
       </c>
       <c r="E6" t="n">
         <v>-1.9444</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6070597116317501</v>
+        <v>0.6070597116317502</v>
       </c>
       <c r="E10" t="n">
         <v>0.4653</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6064505971121524</v>
+        <v>0.6064505971121525</v>
       </c>
       <c r="E11" t="n">
         <v>3.9875</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6008127070733371</v>
+        <v>0.600812707073337</v>
       </c>
       <c r="E16" t="n">
         <v>5.2143</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6008104440157327</v>
+        <v>0.6008104440157328</v>
       </c>
       <c r="E17" t="n">
         <v>0.8974</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6002557000981712</v>
+        <v>0.6002557000981713</v>
       </c>
       <c r="E19" t="n">
         <v>11.1111</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5989595921296487</v>
+        <v>0.5989595921296486</v>
       </c>
       <c r="E21" t="n">
         <v>11.0684</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6252634101084247</v>
+        <v>0.6252634101084248</v>
       </c>
       <c r="E5" t="n">
         <v>1.2653</v>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6212661513283736</v>
+        <v>0.6212661513283735</v>
       </c>
       <c r="E6" t="n">
         <v>-11.1624</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6182365241587863</v>
+        <v>0.6182365241587864</v>
       </c>
       <c r="E8" t="n">
         <v>-6.0203</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6175729827990124</v>
+        <v>0.6175729827990125</v>
       </c>
       <c r="E10" t="n">
         <v>-4.6495</v>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6157477401323457</v>
+        <v>0.6157477401323458</v>
       </c>
       <c r="E12" t="n">
         <v>1.8062</v>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6145153156397486</v>
+        <v>0.6145153156397485</v>
       </c>
       <c r="E14" t="n">
         <v>0.4653</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6120912840112216</v>
+        <v>0.6120912840112215</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5625</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6048249835465236</v>
+        <v>0.6048249835465237</v>
       </c>
       <c r="E21" t="n">
         <v>-2.8333</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7185221359916382</v>
+        <v>0.7185221359916381</v>
       </c>
       <c r="E2" t="n">
         <v>29.9202</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.62602484451345</v>
+        <v>0.6260248445134498</v>
       </c>
       <c r="E15" t="n">
         <v>10.0175</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.624523301879696</v>
+        <v>0.6245233018796961</v>
       </c>
       <c r="E17" t="n">
         <v>-2.6301</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6237274577168136</v>
+        <v>0.6237274577168135</v>
       </c>
       <c r="E18" t="n">
         <v>2.5253</v>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.622651732450789</v>
+        <v>0.6226517324507889</v>
       </c>
       <c r="E19" t="n">
         <v>11.4803</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6192863392847093</v>
+        <v>0.6192863392847094</v>
       </c>
       <c r="E21" t="n">
         <v>2.5357</v>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6562785493366309</v>
+        <v>0.6562785493366308</v>
       </c>
       <c r="E4" t="n">
         <v>36.5337</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6473121952324685</v>
+        <v>0.6473121952324683</v>
       </c>
       <c r="E6" t="n">
         <v>0.2667</v>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6462150926000385</v>
+        <v>0.6462150926000386</v>
       </c>
       <c r="E7" t="n">
         <v>-12.8983</v>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6439735751831174</v>
+        <v>0.6439735751831173</v>
       </c>
       <c r="E9" t="n">
         <v>3.6865</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6347524087875427</v>
+        <v>0.6347524087875428</v>
       </c>
       <c r="E12" t="n">
         <v>3.0182</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6346679001483575</v>
+        <v>0.6346679001483574</v>
       </c>
       <c r="E13" t="n">
         <v>-1.2115</v>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6273118271356175</v>
+        <v>0.6273118271356176</v>
       </c>
       <c r="E15" t="n">
         <v>-1.9953</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6225147972735467</v>
+        <v>0.6225147972735466</v>
       </c>
       <c r="E17" t="n">
         <v>-2.291</v>

--- a/results/reports/year_2023_report.xlsx
+++ b/results/reports/year_2023_report.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6557624896387573</v>
+        <v>0.6557624896387574</v>
       </c>
       <c r="E5" t="n">
         <v>7.5</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6427200799579919</v>
+        <v>0.642720079957992</v>
       </c>
       <c r="E7" t="n">
         <v>0.0246</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6379122631440797</v>
+        <v>0.6379122631440798</v>
       </c>
       <c r="E8" t="n">
         <v>0.7039</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6313900942822023</v>
+        <v>0.6313900942822022</v>
       </c>
       <c r="E11" t="n">
         <v>-4.3376</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6238255883323253</v>
+        <v>0.6238255883323252</v>
       </c>
       <c r="E17" t="n">
         <v>21.7178</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6145131260028309</v>
+        <v>0.6145131260028308</v>
       </c>
       <c r="E20" t="n">
         <v>3.6483</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6810700445173343</v>
+        <v>0.6810700445173342</v>
       </c>
       <c r="E3" t="n">
         <v>17.8133</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6578335543160582</v>
+        <v>0.6578335543160579</v>
       </c>
       <c r="E5" t="n">
         <v>1.8706</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6513309719603886</v>
+        <v>0.6513309719603885</v>
       </c>
       <c r="E8" t="n">
         <v>-0.8502999999999999</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6356739032283468</v>
+        <v>0.6356739032283467</v>
       </c>
       <c r="E12" t="n">
         <v>0.0055</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7071030571581223</v>
+        <v>0.7071030571581224</v>
       </c>
       <c r="E3" t="n">
         <v>-1.4945</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6835740078668385</v>
+        <v>0.6835740078668384</v>
       </c>
       <c r="E4" t="n">
         <v>0.2311</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6636561994670438</v>
+        <v>0.6636561994670437</v>
       </c>
       <c r="E8" t="n">
         <v>1.2986</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6550090283565431</v>
+        <v>0.6550090283565432</v>
       </c>
       <c r="E13" t="n">
         <v>-1.5517</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6473026281811805</v>
+        <v>0.6473026281811803</v>
       </c>
       <c r="E17" t="n">
         <v>0.3934</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.645815622527444</v>
+        <v>0.6458156225274437</v>
       </c>
       <c r="E18" t="n">
         <v>-9.2056</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6422519559674821</v>
+        <v>0.642251955967482</v>
       </c>
       <c r="E20" t="n">
         <v>-3.9025</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7310606960004155</v>
+        <v>0.7310606960004157</v>
       </c>
       <c r="E2" t="n">
         <v>7.8353</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7069626671565215</v>
+        <v>0.7069626671565216</v>
       </c>
       <c r="E4" t="n">
         <v>17.292</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7049426620704718</v>
+        <v>0.7049426620704717</v>
       </c>
       <c r="E5" t="n">
         <v>1.7172</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6703433882632001</v>
+        <v>0.6703433882631999</v>
       </c>
       <c r="E11" t="n">
         <v>-5.6868</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6653793821244196</v>
+        <v>0.6653793821244194</v>
       </c>
       <c r="E13" t="n">
         <v>3.1537</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6473375465315461</v>
+        <v>0.6473375465315462</v>
       </c>
       <c r="E19" t="n">
         <v>2.8149</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6470691514393281</v>
+        <v>0.6470691514393279</v>
       </c>
       <c r="E20" t="n">
         <v>-1.7964</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6814544030983515</v>
+        <v>0.6814544030983517</v>
       </c>
       <c r="E4" t="n">
         <v>13.6211</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6692266413980323</v>
+        <v>0.6692266413980321</v>
       </c>
       <c r="E7" t="n">
         <v>4.7088</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6551909873595271</v>
+        <v>0.655190987359527</v>
       </c>
       <c r="E9" t="n">
         <v>12.9084</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.652381232565697</v>
+        <v>0.6523812325656972</v>
       </c>
       <c r="E11" t="n">
         <v>9.3207</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6504288262724244</v>
+        <v>0.6504288262724245</v>
       </c>
       <c r="E12" t="n">
         <v>4.8757</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6487764907334257</v>
+        <v>0.6487764907334258</v>
       </c>
       <c r="E13" t="n">
         <v>3.5943</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6354468549706316</v>
+        <v>0.6354468549706317</v>
       </c>
       <c r="E17" t="n">
         <v>7.059</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6304364709871608</v>
+        <v>0.6304364709871609</v>
       </c>
       <c r="E19" t="n">
         <v>-3.8462</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7164118035899759</v>
+        <v>0.7164118035899757</v>
       </c>
       <c r="E2" t="n">
         <v>10.7741</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7066997074183062</v>
+        <v>0.7066997074183063</v>
       </c>
       <c r="E3" t="n">
         <v>24.3687</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6983909997064919</v>
+        <v>0.698390999706492</v>
       </c>
       <c r="E4" t="n">
         <v>1.8452</v>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6488892108101088</v>
+        <v>0.6488892108101086</v>
       </c>
       <c r="E7" t="n">
         <v>3.4414</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.646786731793965</v>
+        <v>0.6467867317939648</v>
       </c>
       <c r="E8" t="n">
         <v>15.9988</v>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.640268919220524</v>
+        <v>0.6402689192205239</v>
       </c>
       <c r="E9" t="n">
         <v>7.5781</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6327229434457805</v>
+        <v>0.6327229434457806</v>
       </c>
       <c r="E11" t="n">
         <v>12.7411</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6314211026624873</v>
+        <v>0.6314211026624874</v>
       </c>
       <c r="E12" t="n">
         <v>1.4367</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6297994076174557</v>
+        <v>0.6297994076174556</v>
       </c>
       <c r="E14" t="n">
         <v>2.8758</v>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6283961285028269</v>
+        <v>0.6283961285028268</v>
       </c>
       <c r="E15" t="n">
         <v>9.603899999999999</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6265492272360806</v>
+        <v>0.6265492272360805</v>
       </c>
       <c r="E16" t="n">
         <v>2.0893</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6196470325976839</v>
+        <v>0.6196470325976841</v>
       </c>
       <c r="E20" t="n">
         <v>3.1328</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6581899335493189</v>
+        <v>0.6581899335493188</v>
       </c>
       <c r="E3" t="n">
         <v>23.0218</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6476239926355225</v>
+        <v>0.6476239926355227</v>
       </c>
       <c r="E4" t="n">
         <v>-1.7231</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6408925198564749</v>
+        <v>0.6408925198564751</v>
       </c>
       <c r="E7" t="n">
         <v>0.4777</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6360217776431228</v>
+        <v>0.636021777643123</v>
       </c>
       <c r="E8" t="n">
         <v>17.129</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6346123340166647</v>
+        <v>0.6346123340166648</v>
       </c>
       <c r="E9" t="n">
         <v>13.0849</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6327553375519636</v>
+        <v>0.6327553375519637</v>
       </c>
       <c r="E10" t="n">
         <v>-3.6518</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6233017686448501</v>
+        <v>0.6233017686448502</v>
       </c>
       <c r="E14" t="n">
         <v>8.9649</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6173950121703803</v>
+        <v>0.6173950121703804</v>
       </c>
       <c r="E21" t="n">
         <v>-2.3369</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7059813655057902</v>
+        <v>0.70598136550579</v>
       </c>
       <c r="E3" t="n">
         <v>30.2249</v>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6138240564138102</v>
+        <v>0.6138240564138103</v>
       </c>
       <c r="E14" t="n">
         <v>-17.2401</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6137733103935863</v>
+        <v>0.6137733103935864</v>
       </c>
       <c r="E15" t="n">
         <v>2.2634</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6134619995327852</v>
+        <v>0.6134619995327854</v>
       </c>
       <c r="E17" t="n">
         <v>-12.314</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6599173622480277</v>
+        <v>0.6599173622480276</v>
       </c>
       <c r="E3" t="n">
         <v>2.0305</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6307937036310165</v>
+        <v>0.6307937036310164</v>
       </c>
       <c r="E4" t="n">
         <v>2.6559</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6263371518168699</v>
+        <v>0.6263371518168698</v>
       </c>
       <c r="E5" t="n">
         <v>14.4847</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.616471534303092</v>
+        <v>0.6164715343030922</v>
       </c>
       <c r="E6" t="n">
         <v>-1.9444</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6136062897535993</v>
+        <v>0.6136062897535992</v>
       </c>
       <c r="E7" t="n">
         <v>5.0911</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6064505971121525</v>
+        <v>0.6064505971121524</v>
       </c>
       <c r="E11" t="n">
         <v>3.9875</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.600812707073337</v>
+        <v>0.6008127070733371</v>
       </c>
       <c r="E16" t="n">
         <v>5.2143</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6008104440157328</v>
+        <v>0.6008104440157327</v>
       </c>
       <c r="E17" t="n">
         <v>0.8974</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5994604994927041</v>
+        <v>0.5994604994927039</v>
       </c>
       <c r="E20" t="n">
         <v>3.2712</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6175729827990125</v>
+        <v>0.6175729827990124</v>
       </c>
       <c r="E10" t="n">
         <v>-4.6495</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6120912840112215</v>
+        <v>0.6120912840112216</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5625</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6090366000102307</v>
+        <v>0.6090366000102306</v>
       </c>
       <c r="E18" t="n">
         <v>-8.023199999999999</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6048249835465237</v>
+        <v>0.6048249835465236</v>
       </c>
       <c r="E21" t="n">
         <v>-2.8333</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.632878096477025</v>
+        <v>0.6328780964770249</v>
       </c>
       <c r="E10" t="n">
         <v>-0.8604000000000001</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6302189962328117</v>
+        <v>0.6302189962328115</v>
       </c>
       <c r="E12" t="n">
         <v>-3.8534</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6274512295736758</v>
+        <v>0.6274512295736757</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8121</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6260248445134498</v>
+        <v>0.62602484451345</v>
       </c>
       <c r="E15" t="n">
         <v>10.0175</v>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6226517324507889</v>
+        <v>0.622651732450789</v>
       </c>
       <c r="E19" t="n">
         <v>11.4803</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6192863392847094</v>
+        <v>0.6192863392847093</v>
       </c>
       <c r="E21" t="n">
         <v>2.5357</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.665541181874453</v>
+        <v>0.6655411818744531</v>
       </c>
       <c r="E3" t="n">
         <v>5.6522</v>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6562785493366308</v>
+        <v>0.6562785493366309</v>
       </c>
       <c r="E4" t="n">
         <v>36.5337</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6513981340606162</v>
+        <v>0.6513981340606163</v>
       </c>
       <c r="E5" t="n">
         <v>1.3136</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6473121952324683</v>
+        <v>0.6473121952324685</v>
       </c>
       <c r="E6" t="n">
         <v>0.2667</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6385961264481272</v>
+        <v>0.6385961264481275</v>
       </c>
       <c r="E10" t="n">
         <v>1.5174</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6347524087875428</v>
+        <v>0.6347524087875427</v>
       </c>
       <c r="E12" t="n">
         <v>3.0182</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6346679001483574</v>
+        <v>0.6346679001483575</v>
       </c>
       <c r="E13" t="n">
         <v>-1.2115</v>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6273118271356176</v>
+        <v>0.6273118271356175</v>
       </c>
       <c r="E15" t="n">
         <v>-1.9953</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6225147972735466</v>
+        <v>0.6225147972735465</v>
       </c>
       <c r="E17" t="n">
         <v>-2.291</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6221299581407702</v>
+        <v>0.6221299581407703</v>
       </c>
       <c r="E18" t="n">
         <v>-2.3877</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6165196425158274</v>
+        <v>0.6165196425158271</v>
       </c>
       <c r="E20" t="n">
         <v>4.336</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6159620269295324</v>
+        <v>0.6159620269295323</v>
       </c>
       <c r="E21" t="n">
         <v>0.2104</v>

--- a/results/reports/year_2023_report.xlsx
+++ b/results/reports/year_2023_report.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6768909645357426</v>
+        <v>0.6768909645357425</v>
       </c>
       <c r="E3" t="n">
         <v>3.5836</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.667969566300143</v>
+        <v>0.6679695663001429</v>
       </c>
       <c r="E4" t="n">
         <v>-3.2418</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6379122631440798</v>
+        <v>0.6379122631440797</v>
       </c>
       <c r="E8" t="n">
         <v>0.7039</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6240659576022883</v>
+        <v>0.6240659576022884</v>
       </c>
       <c r="E16" t="n">
         <v>3.896</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6174135621422449</v>
+        <v>0.6174135621422447</v>
       </c>
       <c r="E18" t="n">
         <v>1.2205</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6145131260028308</v>
+        <v>0.6145131260028309</v>
       </c>
       <c r="E20" t="n">
         <v>3.6483</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6810700445173342</v>
+        <v>0.6810700445173343</v>
       </c>
       <c r="E3" t="n">
         <v>17.8133</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.667341767867575</v>
+        <v>0.6673417678675752</v>
       </c>
       <c r="E4" t="n">
         <v>-2.5786</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6513309719603885</v>
+        <v>0.6513309719603886</v>
       </c>
       <c r="E8" t="n">
         <v>-0.8502999999999999</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6481902691372153</v>
+        <v>0.6481902691372154</v>
       </c>
       <c r="E9" t="n">
         <v>-2.0464</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6456307937639589</v>
+        <v>0.6456307937639587</v>
       </c>
       <c r="E10" t="n">
         <v>14.3791</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6276576752385961</v>
+        <v>0.6276576752385959</v>
       </c>
       <c r="E18" t="n">
         <v>15.9695</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7237754928486058</v>
+        <v>0.7237754928486057</v>
       </c>
       <c r="E2" t="n">
         <v>16.9643</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6792727401804183</v>
+        <v>0.6792727401804182</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2164</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6675908953809652</v>
+        <v>0.6675908953809651</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7471</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6607942147437804</v>
+        <v>0.6607942147437802</v>
       </c>
       <c r="E10" t="n">
         <v>-0.9519</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6590737076671257</v>
+        <v>0.6590737076671256</v>
       </c>
       <c r="E11" t="n">
         <v>-2.2922</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6550090283565432</v>
+        <v>0.6550090283565431</v>
       </c>
       <c r="E13" t="n">
         <v>-1.5517</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6523600133488828</v>
+        <v>0.6523600133488827</v>
       </c>
       <c r="E14" t="n">
         <v>-4.4298</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6519666660255234</v>
+        <v>0.6519666660255232</v>
       </c>
       <c r="E15" t="n">
         <v>-1.9407</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6473026281811803</v>
+        <v>0.6473026281811805</v>
       </c>
       <c r="E17" t="n">
         <v>0.3934</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6458156225274437</v>
+        <v>0.645815622527444</v>
       </c>
       <c r="E18" t="n">
         <v>-9.2056</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7273033911862942</v>
+        <v>0.7273033911862941</v>
       </c>
       <c r="E3" t="n">
         <v>26.0108</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7069626671565216</v>
+        <v>0.7069626671565215</v>
       </c>
       <c r="E4" t="n">
         <v>17.292</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6972991423386929</v>
+        <v>0.6972991423386931</v>
       </c>
       <c r="E6" t="n">
         <v>4.3834</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6703433882631999</v>
+        <v>0.6703433882632001</v>
       </c>
       <c r="E11" t="n">
         <v>-5.6868</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6667728353133643</v>
+        <v>0.6667728353133642</v>
       </c>
       <c r="E12" t="n">
         <v>-5.3237</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6653793821244194</v>
+        <v>0.6653793821244196</v>
       </c>
       <c r="E13" t="n">
         <v>3.1537</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.651380948016413</v>
+        <v>0.6513809480164129</v>
       </c>
       <c r="E18" t="n">
         <v>2.1548</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6473375465315462</v>
+        <v>0.6473375465315461</v>
       </c>
       <c r="E19" t="n">
         <v>2.8149</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6443636073720022</v>
+        <v>0.644363607372002</v>
       </c>
       <c r="E21" t="n">
         <v>1.6573</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6814544030983517</v>
+        <v>0.6814544030983515</v>
       </c>
       <c r="E4" t="n">
         <v>13.6211</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6755804101474052</v>
+        <v>0.6755804101474054</v>
       </c>
       <c r="E5" t="n">
         <v>6.4188</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6354468549706317</v>
+        <v>0.6354468549706316</v>
       </c>
       <c r="E17" t="n">
         <v>7.059</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6304364709871609</v>
+        <v>0.6304364709871608</v>
       </c>
       <c r="E19" t="n">
         <v>-3.8462</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7164118035899757</v>
+        <v>0.7164118035899756</v>
       </c>
       <c r="E2" t="n">
         <v>10.7741</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7066997074183063</v>
+        <v>0.7066997074183062</v>
       </c>
       <c r="E3" t="n">
         <v>24.3687</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6467867317939648</v>
+        <v>0.646786731793965</v>
       </c>
       <c r="E8" t="n">
         <v>15.9988</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6400747176260287</v>
+        <v>0.6400747176260286</v>
       </c>
       <c r="E10" t="n">
         <v>2.3933</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6314211026624874</v>
+        <v>0.6314211026624872</v>
       </c>
       <c r="E12" t="n">
         <v>1.4367</v>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6283961285028268</v>
+        <v>0.6283961285028269</v>
       </c>
       <c r="E15" t="n">
         <v>9.603899999999999</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6265492272360805</v>
+        <v>0.6265492272360806</v>
       </c>
       <c r="E16" t="n">
         <v>2.0893</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6196470325976841</v>
+        <v>0.6196470325976842</v>
       </c>
       <c r="E20" t="n">
         <v>3.1328</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6701328279678723</v>
+        <v>0.6701328279678725</v>
       </c>
       <c r="E2" t="n">
         <v>14.8148</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6581899335493188</v>
+        <v>0.6581899335493189</v>
       </c>
       <c r="E3" t="n">
         <v>23.0218</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6408925198564751</v>
+        <v>0.6408925198564749</v>
       </c>
       <c r="E7" t="n">
         <v>0.4777</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6173950121703804</v>
+        <v>0.6173950121703803</v>
       </c>
       <c r="E21" t="n">
         <v>-2.3369</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6931511315194469</v>
+        <v>0.693151131519447</v>
       </c>
       <c r="E4" t="n">
         <v>2.8636</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6287887167460402</v>
+        <v>0.6287887167460401</v>
       </c>
       <c r="E7" t="n">
         <v>-5.067</v>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6138240564138103</v>
+        <v>0.6138240564138102</v>
       </c>
       <c r="E14" t="n">
         <v>-17.2401</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6134619995327854</v>
+        <v>0.6134619995327852</v>
       </c>
       <c r="E17" t="n">
         <v>-12.314</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6599173622480276</v>
+        <v>0.6599173622480277</v>
       </c>
       <c r="E3" t="n">
         <v>2.0305</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6307937036310164</v>
+        <v>0.6307937036310165</v>
       </c>
       <c r="E4" t="n">
         <v>2.6559</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6263371518168698</v>
+        <v>0.6263371518168699</v>
       </c>
       <c r="E5" t="n">
         <v>14.4847</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6164715343030922</v>
+        <v>0.6164715343030921</v>
       </c>
       <c r="E6" t="n">
         <v>-1.9444</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6136062897535992</v>
+        <v>0.6136062897535993</v>
       </c>
       <c r="E7" t="n">
         <v>5.0911</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6070597116317502</v>
+        <v>0.6070597116317501</v>
       </c>
       <c r="E10" t="n">
         <v>0.4653</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6008127070733371</v>
+        <v>0.6008127070733369</v>
       </c>
       <c r="E16" t="n">
         <v>5.2143</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6008104440157327</v>
+        <v>0.6008104440157328</v>
       </c>
       <c r="E17" t="n">
         <v>0.8974</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5994604994927039</v>
+        <v>0.599460499492704</v>
       </c>
       <c r="E20" t="n">
         <v>3.2712</v>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6302614056310527</v>
+        <v>0.6302614056310528</v>
       </c>
       <c r="E4" t="n">
         <v>6.9048</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6252634101084248</v>
+        <v>0.6252634101084247</v>
       </c>
       <c r="E5" t="n">
         <v>1.2653</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6157681055291538</v>
+        <v>0.615768105529154</v>
       </c>
       <c r="E11" t="n">
         <v>-5.6911</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6090366000102306</v>
+        <v>0.6090366000102307</v>
       </c>
       <c r="E18" t="n">
         <v>-8.023199999999999</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6048249835465236</v>
+        <v>0.6048249835465237</v>
       </c>
       <c r="E21" t="n">
         <v>-2.8333</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6302189962328115</v>
+        <v>0.6302189962328116</v>
       </c>
       <c r="E12" t="n">
         <v>-3.8534</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6274512295736757</v>
+        <v>0.6274512295736758</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8121</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.62602484451345</v>
+        <v>0.6260248445134498</v>
       </c>
       <c r="E15" t="n">
         <v>10.0175</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6245233018796961</v>
+        <v>0.6245233018796962</v>
       </c>
       <c r="E17" t="n">
         <v>-2.6301</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6655411818744531</v>
+        <v>0.665541181874453</v>
       </c>
       <c r="E3" t="n">
         <v>5.6522</v>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6562785493366309</v>
+        <v>0.6562785493366308</v>
       </c>
       <c r="E4" t="n">
         <v>36.5337</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6513981340606163</v>
+        <v>0.6513981340606162</v>
       </c>
       <c r="E5" t="n">
         <v>1.3136</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6473121952324685</v>
+        <v>0.6473121952324683</v>
       </c>
       <c r="E6" t="n">
         <v>0.2667</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6385961264481275</v>
+        <v>0.6385961264481274</v>
       </c>
       <c r="E10" t="n">
         <v>1.5174</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.635630198621285</v>
+        <v>0.6356301986212851</v>
       </c>
       <c r="E11" t="n">
         <v>-11.8964</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6347524087875427</v>
+        <v>0.6347524087875428</v>
       </c>
       <c r="E12" t="n">
         <v>3.0182</v>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6273118271356175</v>
+        <v>0.6273118271356176</v>
       </c>
       <c r="E15" t="n">
         <v>-1.9953</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6225147972735465</v>
+        <v>0.6225147972735466</v>
       </c>
       <c r="E17" t="n">
         <v>-2.291</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.619938109411729</v>
+        <v>0.6199381094117291</v>
       </c>
       <c r="E19" t="n">
         <v>-4.9519</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6165196425158271</v>
+        <v>0.6165196425158274</v>
       </c>
       <c r="E20" t="n">
         <v>4.336</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6159620269295323</v>
+        <v>0.6159620269295324</v>
       </c>
       <c r="E21" t="n">
         <v>0.2104</v>
